--- a/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512413_ELIMINATORIAS18FINAL_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/individual/NP_play_by_play_2512413_ELIMINATORIAS18FINAL_PROCESSED.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.077199999999999</v>
+        <v>7.1013</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6004</v>
+        <v>5.1117</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4768</v>
+        <v>1.9895</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6085</v>
+        <v>2.609</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5332</v>
+        <v>1.5414</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0753</v>
+        <v>1.0676</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1764</v>
+        <v>3.2241</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4257</v>
+        <v>2.4687</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7508</v>
+        <v>0.7553</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.615</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8925</v>
+        <v>-0.9273</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3245</v>
+        <v>0.3122</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2776</v>
+        <v>3.2392</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.2776</v>
+        <v>3.2392</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3588</v>
+        <v>0.407</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6978</v>
+        <v>1.1349</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.339</v>
+        <v>-0.7279</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7262</v>
+        <v>0.7528</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.434</v>
+        <v>6.131</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8046</v>
+        <v>2.0088</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6295</v>
+        <v>4.1222</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8851</v>
+        <v>3.5196</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9845</v>
+        <v>0.9106</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9006</v>
+        <v>2.609</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8606</v>
+        <v>2.8499</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7025</v>
+        <v>0.5531</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1581</v>
+        <v>2.2968</v>
       </c>
       <c r="M3" t="n">
+        <v>0.6697</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="P3" t="n">
         <v>2.0245</v>
       </c>
-      <c r="N3" t="n">
-        <v>1.2819</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.7426</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.0242</v>
-      </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.0123</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0242</v>
+        <v>3.0368</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6923</v>
+        <v>0.2427</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.1711</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8228</v>
+        <v>0.0716</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8324</v>
+        <v>0.3442</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0744</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2421</v>
+        <v>0.3442</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.9298</v>
+        <v>5.7594</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5584</v>
+        <v>2.3841</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3714</v>
+        <v>3.3753</v>
       </c>
       <c r="G4" t="n">
-        <v>3.517</v>
+        <v>2.8636</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9361</v>
+        <v>1.9771</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5809</v>
+        <v>0.8865</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8028</v>
+        <v>0.8702</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5464</v>
+        <v>0.7112000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2564</v>
+        <v>0.159</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7141999999999999</v>
+        <v>1.9934</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3897</v>
+        <v>1.2659</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3245</v>
+        <v>0.7275</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0485</v>
+        <v>1.0123</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0242</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.0727</v>
+        <v>1.0123</v>
       </c>
       <c r="S4" t="n">
-        <v>0.016</v>
+        <v>1.0375</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2202</v>
+        <v>0.4169</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2363</v>
+        <v>0.6206</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3482</v>
+        <v>0.846</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.097</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3482</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="5">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.3276</v>
+        <v>5.1781</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3763</v>
+        <v>2.2111</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9513</v>
+        <v>2.9669</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2562</v>
+        <v>1.2718</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2624</v>
+        <v>-1.2462</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5186</v>
+        <v>2.5179</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1275</v>
+        <v>1.1947</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.9273</v>
+        <v>-0.8726</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0548</v>
+        <v>2.0673</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1288</v>
+        <v>0.0771</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3351</v>
+        <v>-0.3736</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4639</v>
+        <v>0.4507</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4097</v>
+        <v>0.4049</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4824</v>
+        <v>3.4417</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8802</v>
+        <v>-0.0692</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2202</v>
+        <v>0.4826</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6599</v>
+        <v>-0.5518</v>
       </c>
       <c r="V5" t="n">
-        <v>3.5418</v>
+        <v>3.5706</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5418</v>
+        <v>3.5706</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. MORENO TRUJILLO</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4853</v>
+        <v>3.8556</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1112</v>
+        <v>3.3995</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3741</v>
+        <v>0.4561</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5618</v>
+        <v>5.1517</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1079</v>
+        <v>-1.7392</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4538</v>
+        <v>6.891</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2898</v>
+        <v>3.8515</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5786</v>
+        <v>-2.2942</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7113</v>
+        <v>6.1458</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2719</v>
+        <v>1.3002</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5294</v>
+        <v>0.555</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7426</v>
+        <v>0.7452</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6388</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.0727</v>
+        <v>-2.0245</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4339</v>
+        <v>2.6319</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.028</v>
+        <v>-0.4623</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3038</v>
+        <v>0.3823</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3318</v>
+        <v>-0.8446</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5903</v>
+        <v>-1.4411</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5903</v>
+        <v>1.1902</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.6313</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>A. MORENO TRUJILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4779</v>
+        <v>2.6969</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9081</v>
+        <v>0.1157</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5698</v>
+        <v>2.5812</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0409</v>
+        <v>3.5955</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8786</v>
+        <v>2.1524</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1623</v>
+        <v>1.4431</v>
       </c>
       <c r="J7" t="n">
-        <v>0.997</v>
+        <v>2.3533</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6002</v>
+        <v>1.6377</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6032</v>
+        <v>0.7156</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0439</v>
+        <v>1.2422</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2784</v>
+        <v>0.5147</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7655</v>
+        <v>0.7275</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0485</v>
+        <v>-1.6196</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.0368</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0485</v>
+        <v>1.4172</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2656</v>
+        <v>0.126</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6075</v>
+        <v>0.2041</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3419</v>
+        <v>-0.0781</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8771</v>
+        <v>0.5951</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6965</v>
+        <v>0.5951</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1806</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4612</v>
+        <v>2.1619</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3893</v>
+        <v>0.5033</v>
       </c>
       <c r="F8" t="n">
-        <v>0.07190000000000001</v>
+        <v>1.6586</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1315</v>
+        <v>2.034</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7338</v>
+        <v>1.8779</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8653</v>
+        <v>0.1561</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7812</v>
+        <v>1.0308</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.3187</v>
+        <v>1.6199</v>
       </c>
       <c r="L8" t="n">
-        <v>6.0998</v>
+        <v>-0.5891</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3503</v>
+        <v>1.0032</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5849</v>
+        <v>0.258</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7655</v>
+        <v>0.7452</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6145</v>
+        <v>2.0245</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0485</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.663</v>
+        <v>2.0245</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8622</v>
+        <v>-0.0181</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.524</v>
+        <v>0.1608</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.3382</v>
+        <v>-0.1789</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4227</v>
+        <v>-1.8785</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1806</v>
+        <v>-0.6883</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.6033</v>
+        <v>-1.1902</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3081</v>
+        <v>1.0344</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.9836</v>
+        <v>-2.7469</v>
       </c>
       <c r="F9" t="n">
-        <v>4.2916</v>
+        <v>3.7812</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2556</v>
+        <v>-0.2578</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9337</v>
+        <v>-0.9293</v>
       </c>
       <c r="I9" t="n">
-        <v>0.678</v>
+        <v>0.6715</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.5879</v>
+        <v>-1.5428</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1282</v>
+        <v>-1.0892</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4597</v>
+        <v>-0.4536</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3323</v>
+        <v>1.285</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1946</v>
+        <v>0.1599</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1377</v>
+        <v>1.1251</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R9" t="n">
-        <v>2.663</v>
+        <v>2.6319</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6206</v>
+        <v>0.1099</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.917</v>
+        <v>0.2455</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2963</v>
+        <v>-0.1356</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.4544</v>
+        <v>-0.4374</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4544</v>
+        <v>-0.4374</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0377</v>
+        <v>0.0633</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1687</v>
+        <v>0.1913</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2787</v>
+        <v>0.2768</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1216,31 +1216,31 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2787</v>
+        <v>0.2768</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2507</v>
+        <v>-0.2185</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1197</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6591</v>
+        <v>-0.6288</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8278</v>
+        <v>-0.8202</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1687</v>
+        <v>0.1913</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6132</v>
+        <v>-0.6128</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4181</v>
+        <v>-0.4153</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08359999999999999</v>
+        <v>0.0793</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2787</v>
+        <v>0.2768</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2507</v>
+        <v>-0.2185</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1197</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1927</v>
+        <v>-1.3997</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9934</v>
+        <v>-3.0284</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8007</v>
+        <v>1.6287</v>
       </c>
       <c r="G12" t="n">
-        <v>0.196</v>
+        <v>0.2317</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6945</v>
+        <v>-1.6809</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8904</v>
+        <v>1.9126</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0951</v>
+        <v>-0.0015</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.22</v>
+        <v>-1.1689</v>
       </c>
       <c r="L12" t="n">
-        <v>1.125</v>
+        <v>1.1674</v>
       </c>
       <c r="M12" t="n">
-        <v>0.291</v>
+        <v>0.2332</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4744</v>
+        <v>-0.512</v>
       </c>
       <c r="O12" t="n">
-        <v>0.7655</v>
+        <v>0.7452</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8436</v>
+        <v>-1.8221</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R12" t="n">
-        <v>3.2776</v>
+        <v>3.2392</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9391</v>
+        <v>0.6926</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0423</v>
+        <v>0.8441</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1032</v>
+        <v>-0.1516</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4841</v>
+        <v>-0.5019</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6647</v>
+        <v>-1.6921</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.6833</v>
+        <v>-1.6411</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.852</v>
+        <v>-1.8324</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1687</v>
+        <v>0.1913</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7526</v>
+        <v>-0.7512</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8919</v>
+        <v>-0.8895999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1394</v>
+        <v>0.1384</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6968</v>
+        <v>-0.6921</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0558</v>
+        <v>-0.0591</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1952</v>
+        <v>-0.1975</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1394</v>
+        <v>0.1384</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1113</v>
+        <v>-0.08</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.131</v>
+        <v>-0.1281</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0196</v>
+        <v>0.048</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>30.0037</v>
+        <v>30.3123</v>
       </c>
       <c r="E14" t="n">
-        <v>5.960500000000001</v>
+        <v>7.1782</v>
       </c>
       <c r="F14" t="n">
-        <v>24.04320000000001</v>
+        <v>23.13359999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>19.6592</v>
+        <v>19.7344</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5336</v>
+        <v>1.5792</v>
       </c>
       <c r="I14" t="n">
-        <v>18.1252</v>
+        <v>18.1552</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9587</v>
+        <v>12.446</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5623999999999997</v>
+        <v>0.8736000000000003</v>
       </c>
       <c r="L14" t="n">
-        <v>11.3965</v>
+        <v>11.5724</v>
       </c>
       <c r="M14" t="n">
-        <v>7.7003</v>
+        <v>7.2885</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9712999999999998</v>
+        <v>0.7056</v>
       </c>
       <c r="O14" t="n">
-        <v>6.7291</v>
+        <v>6.582799999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>7.169600000000001</v>
+        <v>7.085900000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.3877</v>
+        <v>-16.1963</v>
       </c>
       <c r="R14" t="n">
-        <v>23.55729999999999</v>
+        <v>23.2822</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2681</v>
+        <v>1.5491</v>
       </c>
       <c r="T14" t="n">
-        <v>3.246499999999999</v>
+        <v>3.658</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9784</v>
+        <v>-2.1091</v>
       </c>
       <c r="V14" t="n">
-        <v>1.9068</v>
+        <v>1.943</v>
       </c>
       <c r="W14" t="n">
-        <v>7.143</v>
+        <v>7.2702</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.2363</v>
+        <v>-5.3271</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2735</v>
+        <v>2.4378</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2812</v>
+        <v>2.6017</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0078</v>
+        <v>-0.164</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1353</v>
+        <v>0.1077</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9755</v>
+        <v>0.9689</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8401</v>
+        <v>-0.8613</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3411</v>
+        <v>1.3666</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6693</v>
+        <v>0.6908</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6718</v>
+        <v>0.6758</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2057</v>
+        <v>-1.2589</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3062</v>
+        <v>0.2782</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5119</v>
+        <v>-1.5371</v>
       </c>
       <c r="P15" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6388</v>
+        <v>1.6196</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0755</v>
+        <v>0.2846</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1078</v>
+        <v>0.3891</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0323</v>
+        <v>-0.1045</v>
       </c>
       <c r="V15" t="n">
-        <v>0.4238</v>
+        <v>0.4259</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8324</v>
+        <v>0.846</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.4085</v>
+        <v>-0.4201</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7151</v>
+        <v>0.5454</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1612</v>
+        <v>1.0528</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4461</v>
+        <v>-0.5074</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1934</v>
+        <v>2.1977</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9445</v>
+        <v>3.9718</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7511</v>
+        <v>-1.7742</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3434</v>
+        <v>3.3974</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3038</v>
+        <v>3.3577</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0395</v>
+        <v>0.0398</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1499</v>
+        <v>-1.1998</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6407</v>
+        <v>0.6141</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7906</v>
+        <v>-1.8139</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.6145</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2412</v>
+        <v>0.0636</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2146</v>
+        <v>0.024</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0267</v>
+        <v>0.0396</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.105</v>
+        <v>-1.1085</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3482</v>
+        <v>-0.3442</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.7568</v>
+        <v>-0.7643</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0388</v>
+        <v>-0.3508</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.0536</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4678</v>
+        <v>-0.4044</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4953</v>
+        <v>-1.4838</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2619</v>
+        <v>-0.2572</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2334</v>
+        <v>-1.2266</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5931</v>
+        <v>-0.5516</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1287</v>
+        <v>0.1567</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7218</v>
+        <v>-0.7083</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9022</v>
+        <v>-0.9322</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3906</v>
+        <v>-0.4139</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.5183</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4339</v>
+        <v>1.4172</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3907</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1482</v>
+        <v>0.6297</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7575</v>
+        <v>-0.6384</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9385</v>
+        <v>0.9393</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1806</v>
+        <v>1.1902</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2421</v>
+        <v>-0.2509</v>
       </c>
     </row>
     <row r="18">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0436</v>
+        <v>-0.9923</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3365</v>
+        <v>-1.5184</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2929</v>
+        <v>0.5261</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4703</v>
+        <v>-1.4525</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2767</v>
+        <v>-1.2845</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1935</v>
+        <v>-0.168</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5071</v>
+        <v>-0.4399</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8023</v>
+        <v>-0.7724</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2952</v>
+        <v>0.3325</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9631</v>
+        <v>-1.0126</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4744</v>
+        <v>-0.512</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4887</v>
+        <v>-0.5006</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4339</v>
+        <v>-1.4172</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2776</v>
+        <v>-3.2392</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8436</v>
+        <v>1.8221</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3318</v>
+        <v>0.343</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0256</v>
+        <v>0.7196</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6938</v>
+        <v>-0.3766</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5288</v>
+        <v>1.5344</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4227</v>
+        <v>1.4411</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1062</v>
+        <v>0.09320000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3398</v>
+        <v>-2.7845</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5369</v>
+        <v>-1.8486</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.803</v>
+        <v>-0.9358</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4159</v>
+        <v>-1.4291</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2479</v>
+        <v>0.2377</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6638</v>
+        <v>-1.6668</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1037</v>
+        <v>-0.0732</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0253</v>
+        <v>0.0388</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.129</v>
+        <v>-0.112</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3122</v>
+        <v>-1.3559</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2226</v>
+        <v>0.1989</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5348</v>
+        <v>-1.5548</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0485</v>
+        <v>-2.0245</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0242</v>
+        <v>1.0123</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5396</v>
+        <v>0.0268</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3846</v>
+        <v>0.249</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1549</v>
+        <v>-0.2222</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3601</v>
+        <v>-0.37</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3601</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9009</v>
+        <v>-3.4257</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.7953</v>
+        <v>-5.0425</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8944</v>
+        <v>1.6167</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0264</v>
+        <v>-0.0407</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1284</v>
+        <v>-0.1379</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1019</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.189</v>
+        <v>0.2231</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3787</v>
+        <v>-0.3569</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5677</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2154</v>
+        <v>-0.2638</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2504</v>
+        <v>0.219</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4658</v>
+        <v>-0.4829</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.0727</v>
+        <v>-3.0368</v>
       </c>
       <c r="Q20" t="n">
-        <v>-5.1212</v>
+        <v>-5.0613</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6837</v>
+        <v>-0.2293</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1051</v>
+        <v>-0.4553</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4215</v>
+        <v>0.226</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1181</v>
+        <v>-0.119</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2421</v>
+        <v>0.2509</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3601</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="21">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8687</v>
+        <v>-4.8438</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3203</v>
+        <v>-3.1804</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5485</v>
+        <v>-1.6634</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7939</v>
+        <v>-3.8017</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9512</v>
+        <v>-1.9567</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8427</v>
+        <v>-1.845</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0508</v>
+        <v>-2.0365</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3935</v>
+        <v>-1.3842</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6572</v>
+        <v>-0.6523</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7432</v>
+        <v>-1.7651</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5577</v>
+        <v>-0.5725</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.1855</v>
+        <v>-1.1926</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.8194</v>
+        <v>-0.8098</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0242</v>
+        <v>-1.0123</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2048</v>
+        <v>0.2025</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2554</v>
+        <v>-0.2324</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2453</v>
+        <v>-0.1316</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0102</v>
+        <v>-0.1007</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3391</v>
+        <v>-5.1058</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9506</v>
+        <v>-5.0151</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3885</v>
+        <v>-0.0907</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9049</v>
+        <v>-5.0708</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9815</v>
+        <v>-0.9891</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9234</v>
+        <v>-4.0817</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2857</v>
+        <v>-4.9454</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3397</v>
+        <v>-1.485</v>
       </c>
       <c r="L22" t="n">
-        <v>0.054</v>
+        <v>-3.4605</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6192</v>
+        <v>-0.1254</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6418</v>
+        <v>0.4959</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9774</v>
+        <v>-0.6213</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0485</v>
+        <v>1.2147</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.3018</v>
+        <v>-1.2147</v>
       </c>
       <c r="R22" t="n">
-        <v>2.2533</v>
+        <v>2.4294</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7819</v>
+        <v>-0.2345</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3949</v>
+        <v>-0.0452</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.613</v>
+        <v>-0.1892</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1676</v>
+        <v>-1.0152</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2421</v>
+        <v>1.1902</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.4096</v>
+        <v>-2.2054</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3407</v>
+        <v>-6.4634</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5468</v>
+        <v>-3.6822</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2061</v>
+        <v>-2.7812</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.0921</v>
+        <v>-1.9447</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.0032</v>
+        <v>-1.0068</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.0889</v>
+        <v>-0.9379</v>
       </c>
       <c r="J23" t="n">
-        <v>-5.0161</v>
+        <v>-0.2542</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5323</v>
+        <v>-0.3174</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.4838</v>
+        <v>0.0633</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0761</v>
+        <v>-1.6905</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5291</v>
+        <v>-0.6894</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6051</v>
+        <v>-1.0011</v>
       </c>
       <c r="P23" t="n">
-        <v>1.2291</v>
+        <v>-2.0245</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.2291</v>
+        <v>-4.2515</v>
       </c>
       <c r="R23" t="n">
-        <v>2.4582</v>
+        <v>2.227</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4788</v>
+        <v>-0.3145</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4822</v>
+        <v>0.5725</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0034</v>
+        <v>-0.887</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9988</v>
+        <v>-2.1797</v>
       </c>
       <c r="W23" t="n">
-        <v>1.1806</v>
+        <v>0.2509</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1794</v>
+        <v>-2.4306</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.1983</v>
+        <v>-9.008800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.5061</v>
+        <v>-6.5548</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6923</v>
+        <v>-2.4541</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.789</v>
+        <v>-6.8164</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0986</v>
+        <v>-1.1254</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.6903</v>
+        <v>-5.6911</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.0172</v>
+        <v>-3.9747</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6519</v>
+        <v>-0.6335</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.3652</v>
+        <v>-3.3412</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.7718</v>
+        <v>-2.8418</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4467</v>
+        <v>-0.4919</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.3251</v>
+        <v>-2.3499</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.2291</v>
+        <v>-1.2147</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.2776</v>
+        <v>-3.2392</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0485</v>
+        <v>2.0245</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1318</v>
+        <v>-0.9275</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6954</v>
+        <v>0.1572</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4364</v>
+        <v>-1.0847</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.0484</v>
+        <v>-0.0502</v>
       </c>
       <c r="W24" t="n">
-        <v>0.4841</v>
+        <v>0.5019</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5325</v>
+        <v>-0.5521</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-30.0037</v>
+        <v>-29.9919</v>
       </c>
       <c r="E25" t="n">
-        <v>-24.0435</v>
+        <v>-23.1339</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.960599999999999</v>
+        <v>-6.8582</v>
       </c>
       <c r="G25" t="n">
-        <v>-19.6591</v>
+        <v>-19.7343</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5336</v>
+        <v>-1.5792</v>
       </c>
       <c r="I25" t="n">
-        <v>-18.1253</v>
+        <v>-18.1554</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.7002</v>
+        <v>-7.288400000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.9713000000000006</v>
+        <v>-0.7054000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>-6.7288</v>
+        <v>-6.582800000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.9588</v>
+        <v>-12.446</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5621999999999999</v>
+        <v>-0.8735999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-11.3965</v>
+        <v>-11.5725</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.1696</v>
+        <v>-7.0859</v>
       </c>
       <c r="Q25" t="n">
-        <v>-23.5576</v>
+        <v>-23.2819</v>
       </c>
       <c r="R25" t="n">
-        <v>16.3877</v>
+        <v>16.1963</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2682</v>
+        <v>-1.2289</v>
       </c>
       <c r="T25" t="n">
-        <v>1.9785</v>
+        <v>2.109</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.2465</v>
+        <v>-3.3377</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.906900000000001</v>
+        <v>-1.943</v>
       </c>
       <c r="W25" t="n">
-        <v>5.2364</v>
+        <v>5.326999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.1429</v>
+        <v>-7.2702</v>
       </c>
     </row>
   </sheetData>
